--- a/02_加值成品/九下/九下2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-4_三種難度測驗卷.xlsx
@@ -1394,27 +1394,27 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>線圈匝數越多感應電流？</t>
+          <t>磁鐵停在線圈中不動時有感應電流嗎？</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>法拉第</t>
+          <t>為零</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>感應電流</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>為零</t>
+          <t>發生變化</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>越大</t>
+          <t>沒有</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>匝數：線圈繞的圈數越多，累積產生的感應電流也會越大</t>
+          <t>要有變化才有：感應電流來自穿過線圈的磁場「改變」，磁鐵停著不動時磁場沒有變化，所以不會產生感應電流</t>
         </is>
       </c>
     </row>
